--- a/bousai_app/data/board_data.xlsx
+++ b/bousai_app/data/board_data.xlsx
@@ -1,48 +1,286 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merid\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68DB7D5-4863-48BF-A13C-A369BC6E20C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="被害状況地図" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="被害状況一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="避難指示" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="派遣職員" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="被害状況地図" sheetId="1" r:id="rId1"/>
+    <sheet name="被害状況一覧" sheetId="2" r:id="rId2"/>
+    <sheet name="避難指示" sheetId="3" r:id="rId3"/>
+    <sheet name="派遣職員" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="70">
+  <si>
+    <t>青森駅周辺の道路冠水エリア</t>
+  </si>
+  <si>
+    <t>浪岡地区の土砂災害警戒エリア</t>
+  </si>
+  <si>
+    <t>浅虫地区の通行規制エリア</t>
+  </si>
+  <si>
+    <t>八甲田周辺の孤立集落確認地点</t>
+  </si>
+  <si>
+    <t>油川地区の停電発生エリア</t>
+  </si>
+  <si>
+    <t>発生日時</t>
+  </si>
+  <si>
+    <t>場所</t>
+  </si>
+  <si>
+    <t>被害内容</t>
+  </si>
+  <si>
+    <t>状況</t>
+  </si>
+  <si>
+    <t>2026年09月16日 09:00</t>
+  </si>
+  <si>
+    <t>青森市中央部</t>
+  </si>
+  <si>
+    <t>道路冠水</t>
+  </si>
+  <si>
+    <t>確認中</t>
+  </si>
+  <si>
+    <t>2026年09月16日 09:20</t>
+  </si>
+  <si>
+    <t>青森駅周辺</t>
+  </si>
+  <si>
+    <t>対応中</t>
+  </si>
+  <si>
+    <t>2026年09月16日 09:45</t>
+  </si>
+  <si>
+    <t>浪岡地区</t>
+  </si>
+  <si>
+    <t>土砂崩れの可能性</t>
+  </si>
+  <si>
+    <t>現地確認中</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:15</t>
+  </si>
+  <si>
+    <t>浅虫地区</t>
+  </si>
+  <si>
+    <t>倒木による通行障害</t>
+  </si>
+  <si>
+    <t>通行止め</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:40</t>
+  </si>
+  <si>
+    <t>八甲田周辺</t>
+  </si>
+  <si>
+    <t>停電</t>
+  </si>
+  <si>
+    <t>復旧作業中</t>
+  </si>
+  <si>
+    <t>2026年09月16日 11:00</t>
+  </si>
+  <si>
+    <t>油川地区</t>
+  </si>
+  <si>
+    <t>河川水位上昇</t>
+  </si>
+  <si>
+    <t>警戒中</t>
+  </si>
+  <si>
+    <t>指示内容</t>
+  </si>
+  <si>
+    <t>発令日時</t>
+  </si>
+  <si>
+    <t>安全な場所へ避難してください</t>
+  </si>
+  <si>
+    <t>2026年09月16日 09:30</t>
+  </si>
+  <si>
+    <t>発令中</t>
+  </si>
+  <si>
+    <t>危険な場所から避難してください</t>
+  </si>
+  <si>
+    <t>土砂災害に備えて避難所へ移動してください</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:00</t>
+  </si>
+  <si>
+    <t>不要不急の外出を控えてください</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:20</t>
+  </si>
+  <si>
+    <t>継続中</t>
+  </si>
+  <si>
+    <t>河川から離れた安全な場所で待機してください</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:50</t>
+  </si>
+  <si>
+    <t>青森市全域</t>
+  </si>
+  <si>
+    <t>最新の防災情報を確認してください</t>
+  </si>
+  <si>
+    <t>2026年09月16日 11:10</t>
+  </si>
+  <si>
+    <t>周知中</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>所属</t>
+  </si>
+  <si>
+    <t>派遣先</t>
+  </si>
+  <si>
+    <t>派遣日時</t>
+  </si>
+  <si>
+    <t>山田 太郎</t>
+  </si>
+  <si>
+    <t>防災課</t>
+  </si>
+  <si>
+    <t>佐藤 花子</t>
+  </si>
+  <si>
+    <t>地域防災課</t>
+  </si>
+  <si>
+    <t>鈴木 一郎</t>
+  </si>
+  <si>
+    <t>土木課</t>
+  </si>
+  <si>
+    <t>高橋 美咲</t>
+  </si>
+  <si>
+    <t>福祉課</t>
+  </si>
+  <si>
+    <t>浅虫地区避難所</t>
+  </si>
+  <si>
+    <t>伊藤 健</t>
+  </si>
+  <si>
+    <t>上下水道課</t>
+  </si>
+  <si>
+    <t>2026年09月16日 10:45</t>
+  </si>
+  <si>
+    <t>渡辺 直子</t>
+  </si>
+  <si>
+    <t>保健予防課</t>
+  </si>
+  <si>
+    <t>青森市民体育館</t>
+  </si>
+  <si>
+    <t>地点ごとの被害状況</t>
+    <rPh sb="0" eb="2">
+      <t>チテン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ヒガイジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象地域</t>
+    <phoneticPr fontId="2"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002556A5"/>
+        <fgColor rgb="FF2556A5"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,84 +296,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,224 +605,390 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>地図</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>青森市中央部の被害状況を確認</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="26" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="26" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="26" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="26" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>発生日時</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>被害内容</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026年09月16日 09:00</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>青森市中央部</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>道路冠水</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>確認中</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>対象地域</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>指示内容</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>発令日時</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>青森市中央部</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>安全な場所へ避難してください</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026年09月16日 09:30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>発令中</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>所属</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>派遣先</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>派遣日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>山田 太郎</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>防災課</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>青森市中央部</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026年09月16日 10:00</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>